--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -1351,7 +1351,7 @@
         <v>113588043</v>
       </c>
       <c r="B8" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -1380,11 +1380,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>

--- a/artfynd/A 60679-2023 artfynd.xlsx
+++ b/artfynd/A 60679-2023 artfynd.xlsx
@@ -1351,7 +1351,7 @@
         <v>113588043</v>
       </c>
       <c r="B8" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
